--- a/data-raw/fsaArcPlc/input_data/fsaMyaPrice/MYA_2025.xlsx
+++ b/data-raw/fsaArcPlc/input_data/fsaMyaPrice/MYA_2025.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EPAS\2014FBIMP\ARC_PLC\Webpage Posting\2026-0812\Program Year 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EPAS\2014FBIMP\ARC_PLC\Webpage Posting\2026-0911\Program Year 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F207D484-727D-40B7-88F6-CF1C8B086BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D51E76-D2D1-427D-99B1-FC1694F69BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MYA Prices" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -25,7 +25,7 @@
     <t>TABLE 1. 2019/20-2025/26 MARKET YEAR AVERAGE (MYA) PRICES</t>
   </si>
   <si>
-    <t>August 12, 2026 1/</t>
+    <t>September 11, 2026 1/</t>
   </si>
   <si>
     <t>Commodity</t>
@@ -94,16 +94,16 @@
     <t>Pound</t>
   </si>
   <si>
+    <t>Corn</t>
+  </si>
+  <si>
+    <t>Sep. 1-Aug. 31</t>
+  </si>
+  <si>
+    <t>September 30, 2026</t>
+  </si>
+  <si>
     <t>P</t>
-  </si>
-  <si>
-    <t>Corn</t>
-  </si>
-  <si>
-    <t>Sep. 1-Aug. 31</t>
-  </si>
-  <si>
-    <t>September 30, 2026</t>
   </si>
   <si>
     <t>Grain Sorghum</t>
@@ -806,21 +806,21 @@
         <v>0.26100000000000001</v>
       </c>
       <c r="K8" s="10">
-        <v>0.23599999999999999</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>16</v>
@@ -847,7 +847,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -855,10 +855,10 @@
         <v>28</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>16</v>
@@ -882,10 +882,10 @@
         <v>4.07</v>
       </c>
       <c r="K10" s="6">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -893,10 +893,10 @@
         <v>29</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>16</v>
@@ -920,10 +920,10 @@
         <v>10</v>
       </c>
       <c r="K11" s="6">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1045,10 +1045,10 @@
         <v>35</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>23</v>
@@ -1072,10 +1072,10 @@
         <v>0.34300000000000003</v>
       </c>
       <c r="K15" s="10">
-        <v>0.25600000000000001</v>
+        <v>0.254</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1083,10 +1083,10 @@
         <v>36</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>23</v>
@@ -1110,10 +1110,10 @@
         <v>0.25600000000000001</v>
       </c>
       <c r="K16" s="10">
-        <v>0.16300000000000001</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1121,10 +1121,10 @@
         <v>37</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>23</v>
@@ -1151,7 +1151,7 @@
         <v>0.23499999999999999</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1197,10 +1197,10 @@
         <v>39</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>23</v>
@@ -1227,7 +1227,7 @@
         <v>0.3075</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1273,10 +1273,10 @@
         <v>41</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>23</v>
@@ -1303,7 +1303,7 @@
         <v>0.20799999999999999</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1311,10 +1311,10 @@
         <v>42</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>23</v>
@@ -1341,7 +1341,7 @@
         <v>0.32</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1349,10 +1349,10 @@
         <v>43</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>23</v>
@@ -1379,7 +1379,7 @@
         <v>0.33</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1390,7 +1390,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>23</v>
@@ -1414,10 +1414,10 @@
         <v>0.34039999999999998</v>
       </c>
       <c r="K24" s="10">
-        <v>0.33889999999999998</v>
+        <v>0.34110000000000001</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1455,7 +1455,7 @@
         <v>0.104</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1490,10 +1490,10 @@
         <v>0.15</v>
       </c>
       <c r="K26" s="10">
-        <v>0.14899999999999999</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1528,10 +1528,10 @@
         <v>0.187</v>
       </c>
       <c r="K27" s="15">
-        <v>0.20200000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="L27" s="17" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">

--- a/data-raw/fsaArcPlc/input_data/fsaMyaPrice/MYA_2025.xlsx
+++ b/data-raw/fsaArcPlc/input_data/fsaMyaPrice/MYA_2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EPAS\2014FBIMP\ARC_PLC\Webpage Posting\2026-0911\Program Year 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EPAS\2014FBIMP\ARC_PLC\Webpage Posting\2026-1009\Program Year 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D51E76-D2D1-427D-99B1-FC1694F69BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F69A85-FCB6-4018-BDDD-7667FEB51512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <t>TABLE 1. 2019/20-2025/26 MARKET YEAR AVERAGE (MYA) PRICES</t>
   </si>
   <si>
-    <t>September 11, 2026 1/</t>
+    <t>October 9, 2026 1/</t>
   </si>
   <si>
     <t>Commodity</t>
@@ -103,64 +103,64 @@
     <t>September 30, 2026</t>
   </si>
   <si>
+    <t>Grain Sorghum</t>
+  </si>
+  <si>
+    <t>Soybeans</t>
+  </si>
+  <si>
+    <t>Dry Peas</t>
+  </si>
+  <si>
+    <t>Jul. 1-Jun. 30</t>
+  </si>
+  <si>
+    <t>July 31, 2026</t>
+  </si>
+  <si>
+    <t>Lentils</t>
+  </si>
+  <si>
+    <t>Canola</t>
+  </si>
+  <si>
+    <t>Large Chickpeas</t>
+  </si>
+  <si>
+    <t>Small Chickpeas</t>
+  </si>
+  <si>
+    <t>Sunflower Seed</t>
+  </si>
+  <si>
+    <t>Flaxseed</t>
+  </si>
+  <si>
+    <t>Mustard Seed</t>
+  </si>
+  <si>
+    <t>Rapeseed</t>
+  </si>
+  <si>
+    <t>Safflower</t>
+  </si>
+  <si>
+    <t>Crambe</t>
+  </si>
+  <si>
+    <t>Sesame Seed</t>
+  </si>
+  <si>
+    <t>Seed Cotton 2/</t>
+  </si>
+  <si>
+    <t>Rice (long grain)</t>
+  </si>
+  <si>
+    <t>October 30, 2026</t>
+  </si>
+  <si>
     <t>P</t>
-  </si>
-  <si>
-    <t>Grain Sorghum</t>
-  </si>
-  <si>
-    <t>Soybeans</t>
-  </si>
-  <si>
-    <t>Dry Peas</t>
-  </si>
-  <si>
-    <t>Jul. 1-Jun. 30</t>
-  </si>
-  <si>
-    <t>July 31, 2026</t>
-  </si>
-  <si>
-    <t>Lentils</t>
-  </si>
-  <si>
-    <t>Canola</t>
-  </si>
-  <si>
-    <t>Large Chickpeas</t>
-  </si>
-  <si>
-    <t>Small Chickpeas</t>
-  </si>
-  <si>
-    <t>Sunflower Seed</t>
-  </si>
-  <si>
-    <t>Flaxseed</t>
-  </si>
-  <si>
-    <t>Mustard Seed</t>
-  </si>
-  <si>
-    <t>Rapeseed</t>
-  </si>
-  <si>
-    <t>Safflower</t>
-  </si>
-  <si>
-    <t>Crambe</t>
-  </si>
-  <si>
-    <t>Sesame Seed</t>
-  </si>
-  <si>
-    <t>Seed Cotton 2/</t>
-  </si>
-  <si>
-    <t>Rice (long grain)</t>
-  </si>
-  <si>
-    <t>October 30, 2026</t>
   </si>
   <si>
     <t>Rice (med/short grain) 3/</t>
@@ -206,16 +206,19 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -844,15 +847,15 @@
         <v>4.24</v>
       </c>
       <c r="K9" s="6">
-        <v>4.1500000000000004</v>
+        <v>4.16</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>25</v>
@@ -882,15 +885,15 @@
         <v>4.07</v>
       </c>
       <c r="K10" s="6">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>25</v>
@@ -923,18 +926,18 @@
         <v>10.5</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>23</v>
@@ -966,13 +969,13 @@
     </row>
     <row r="13" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>23</v>
@@ -1004,13 +1007,13 @@
     </row>
     <row r="14" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>23</v>
@@ -1042,7 +1045,7 @@
     </row>
     <row r="15" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>25</v>
@@ -1072,15 +1075,15 @@
         <v>0.34300000000000003</v>
       </c>
       <c r="K15" s="10">
-        <v>0.254</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>25</v>
@@ -1113,12 +1116,12 @@
         <v>0.16400000000000001</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>25</v>
@@ -1148,21 +1151,21 @@
         <v>0.23799999999999999</v>
       </c>
       <c r="K17" s="10">
-        <v>0.23499999999999999</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>16</v>
@@ -1194,7 +1197,7 @@
     </row>
     <row r="19" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>25</v>
@@ -1224,21 +1227,21 @@
         <v>0.44900000000000001</v>
       </c>
       <c r="K19" s="10">
-        <v>0.3075</v>
+        <v>0.309</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>23</v>
@@ -1270,7 +1273,7 @@
     </row>
     <row r="21" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>25</v>
@@ -1300,15 +1303,15 @@
         <v>0.24299999999999999</v>
       </c>
       <c r="K21" s="10">
-        <v>0.20799999999999999</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>25</v>
@@ -1341,12 +1344,12 @@
         <v>0.32</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>25</v>
@@ -1376,15 +1379,15 @@
         <v>0.54</v>
       </c>
       <c r="K23" s="10">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>21</v>
@@ -1414,21 +1417,21 @@
         <v>0.34039999999999998</v>
       </c>
       <c r="K24" s="10">
-        <v>0.34110000000000001</v>
+        <v>0.34079999999999999</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>23</v>
@@ -1455,7 +1458,7 @@
         <v>0.104</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1466,7 +1469,7 @@
         <v>21</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>23</v>
@@ -1493,7 +1496,7 @@
         <v>0.14699999999999999</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1531,7 +1534,7 @@
         <v>0.2</v>
       </c>
       <c r="L27" s="17" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1609,6 +1612,6 @@
     <mergeCell ref="A31:L31"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="1.6" header="0" footer="0"/>
-  <pageSetup scale="89" orientation="landscape" cellComments="atEnd" horizontalDpi="2400" verticalDpi="2400" r:id="rId1"/>
+  <pageSetup scale="89" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>